--- a/output/observations-summary.xlsx
+++ b/output/observations-summary.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1749" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1771" uniqueCount="123">
   <si>
     <t>Profile</t>
   </si>
@@ -53,6 +53,9 @@
     <t>T-CABS Observation AHI</t>
   </si>
   <si>
+    <t>Observation Category Codes#procedure</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
@@ -189,6 +192,18 @@
   </si>
   <si>
     <t>null#153500</t>
+  </si>
+  <si>
+    <t>t-cabs-observation-beatmungsparameter</t>
+  </si>
+  <si>
+    <t>T-CABS Observation Ventilation Parameter (abstract)</t>
+  </si>
+  <si>
+    <t>t-cabs-observation-beatmungsparametermitkomponenten</t>
+  </si>
+  <si>
+    <t>T-CABS Observation Ventilation Parameter with Components (abstract)</t>
   </si>
   <si>
     <t>t-cabs-observation-bmi</t>
@@ -499,7 +514,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:K159"/>
+  <dimension ref="A1:K161"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -548,3770 +563,3770 @@
         <v>13</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E2" t="s" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F2" t="s" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G2" t="s" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H2" t="s" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I2" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J2" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K2" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C3" t="s" s="2">
         <v>13</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E3" t="s" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F3" t="s" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H3" t="s" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I3" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J3" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C4" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E4" t="s" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F4" t="s" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H4" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I4" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J4" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E5" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F5" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H5" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C6" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E6" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F6" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H6" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I6" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J6" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C7" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E7" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F7" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H7" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I7" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J7" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C8" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D8" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E8" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F8" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H8" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I8" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J8" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C9" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D9" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E9" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F9" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H9" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I9" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J9" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D10" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E10" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F10" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H10" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J10" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C11" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D11" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E11" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="F11" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="G11" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="H11" t="s" s="2">
         <v>37</v>
       </c>
-      <c r="F11" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="G11" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="H11" t="s" s="2">
-        <v>36</v>
-      </c>
       <c r="I11" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D12" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E12" t="s" s="2">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F12" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I12" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C13" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D13" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E13" t="s" s="2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F13" t="s" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H13" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C14" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D14" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E14" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F14" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C15" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D15" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E15" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F15" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I15" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C16" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D16" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E16" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F16" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I16" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C17" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D17" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E17" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F17" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I17" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C18" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D18" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E18" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F18" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I18" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C19" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D19" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E19" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F19" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I19" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C20" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D20" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E20" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F20" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I20" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D21" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E21" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F21" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I21" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C22" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D22" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E22" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F22" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I22" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C23" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D23" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E23" t="s" s="2">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F23" t="s" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I23" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D24" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E24" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F24" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I24" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C25" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D25" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E25" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F25" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I25" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C26" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D26" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E26" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F26" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I26" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C27" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D27" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E27" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F27" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I27" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C28" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D28" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E28" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F28" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I28" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C29" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D29" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E29" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F29" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I29" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C30" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D30" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E30" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F30" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I30" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C31" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D31" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E31" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F31" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I31" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C32" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D32" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E32" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F32" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I32" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C33" t="s" s="2">
         <v>13</v>
       </c>
       <c r="D33" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E33" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F33" t="s" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I33" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C34" t="s" s="2">
         <v>13</v>
       </c>
       <c r="D34" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E34" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F34" t="s" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I34" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C35" t="s" s="2">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D35" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E35" t="s" s="2">
-        <v>61</v>
+        <v>14</v>
       </c>
       <c r="F35" t="s" s="2">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="I35" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>13</v>
+        <v>62</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C36" t="s" s="2">
         <v>13</v>
       </c>
       <c r="D36" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E36" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F36" t="s" s="2">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>43</v>
+        <v>14</v>
       </c>
       <c r="I36" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>30</v>
+        <v>14</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>13</v>
+        <v>64</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="C37" t="s" s="2">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="D37" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E37" t="s" s="2">
-        <v>13</v>
+        <v>66</v>
       </c>
       <c r="F37" t="s" s="2">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I37" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>32</v>
+        <v>14</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="C38" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D38" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E38" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F38" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="I38" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="C39" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D39" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E39" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F39" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I39" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="C40" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D40" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E40" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F40" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="I40" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>13</v>
+        <v>34</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="C41" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D41" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E41" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F41" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="I41" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>45</v>
+        <v>35</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="C42" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D42" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E42" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F42" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="I42" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>47</v>
+        <v>14</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="C43" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D43" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E43" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F43" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I43" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="C44" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D44" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E44" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F44" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I44" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>62</v>
+        <v>14</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C45" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D45" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E45" t="s" s="2">
-        <v>64</v>
+        <v>14</v>
       </c>
       <c r="F45" t="s" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>65</v>
+        <v>14</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="I45" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>13</v>
+        <v>49</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C46" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D46" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E46" t="s" s="2">
-        <v>66</v>
+        <v>14</v>
       </c>
       <c r="F46" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="I46" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>13</v>
+        <v>50</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>13</v>
+        <v>67</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="C47" t="s" s="2">
         <v>13</v>
       </c>
       <c r="D47" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E47" t="s" s="2">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F47" t="s" s="2">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>13</v>
+        <v>70</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="I47" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="B48" t="s" s="2">
         <v>68</v>
       </c>
-      <c r="B48" t="s" s="2">
-        <v>69</v>
-      </c>
       <c r="C48" t="s" s="2">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D48" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E48" t="s" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F48" t="s" s="2">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="I48" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C49" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D49" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E49" t="s" s="2">
-        <v>13</v>
+        <v>72</v>
       </c>
       <c r="F49" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="I49" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>30</v>
+        <v>14</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>13</v>
+        <v>73</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="C50" t="s" s="2">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="D50" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E50" t="s" s="2">
-        <v>13</v>
+        <v>75</v>
       </c>
       <c r="F50" t="s" s="2">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I50" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>32</v>
+        <v>14</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="C51" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D51" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E51" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F51" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="I51" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="C52" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D52" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E52" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F52" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I52" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="C53" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D53" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E53" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F53" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="I53" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>13</v>
+        <v>34</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="C54" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D54" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E54" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F54" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H54" t="s" s="2">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="I54" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>45</v>
+        <v>35</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="C55" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D55" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E55" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F55" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H55" t="s" s="2">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="I55" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>47</v>
+        <v>14</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="C56" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D56" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E56" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F56" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H56" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I56" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="C57" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D57" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E57" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F57" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H57" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I57" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>71</v>
+        <v>14</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C58" t="s" s="2">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D58" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E58" t="s" s="2">
-        <v>73</v>
+        <v>14</v>
       </c>
       <c r="F58" t="s" s="2">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="H58" t="s" s="2">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="I58" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>13</v>
+        <v>49</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C59" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D59" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E59" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F59" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H59" t="s" s="2">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="I59" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>30</v>
+        <v>50</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>13</v>
+        <v>76</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="C60" t="s" s="2">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="D60" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E60" t="s" s="2">
-        <v>13</v>
+        <v>78</v>
       </c>
       <c r="F60" t="s" s="2">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="H60" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I60" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>32</v>
+        <v>14</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="C61" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D61" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E61" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F61" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H61" t="s" s="2">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="I61" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="C62" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D62" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E62" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F62" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H62" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I62" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="C63" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D63" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E63" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F63" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H63" t="s" s="2">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="I63" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>13</v>
+        <v>34</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="C64" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D64" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E64" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F64" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H64" t="s" s="2">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="I64" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>45</v>
+        <v>35</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="C65" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D65" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E65" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F65" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H65" t="s" s="2">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="I65" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>47</v>
+        <v>14</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="C66" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D66" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E66" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F66" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H66" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I66" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="C67" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D67" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E67" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F67" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H67" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I67" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>74</v>
+        <v>14</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C68" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D68" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E68" t="s" s="2">
-        <v>76</v>
+        <v>14</v>
       </c>
       <c r="F68" t="s" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="H68" t="s" s="2">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="I68" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>13</v>
+        <v>49</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="B69" t="s" s="2">
         <v>77</v>
       </c>
-      <c r="B69" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="C69" t="s" s="2">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D69" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E69" t="s" s="2">
-        <v>79</v>
+        <v>14</v>
       </c>
       <c r="F69" t="s" s="2">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="H69" t="s" s="2">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="I69" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>13</v>
+        <v>50</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>13</v>
+        <v>79</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C70" t="s" s="2">
         <v>13</v>
       </c>
       <c r="D70" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E70" t="s" s="2">
-        <v>13</v>
+        <v>81</v>
       </c>
       <c r="F70" t="s" s="2">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="H70" t="s" s="2">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="I70" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>30</v>
+        <v>14</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>13</v>
+        <v>82</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C71" t="s" s="2">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="D71" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E71" t="s" s="2">
-        <v>13</v>
+        <v>84</v>
       </c>
       <c r="F71" t="s" s="2">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="H71" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I71" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>32</v>
+        <v>14</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C72" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D72" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E72" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F72" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H72" t="s" s="2">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="I72" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C73" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D73" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E73" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F73" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H73" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I73" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C74" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D74" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E74" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F74" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H74" t="s" s="2">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="I74" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>13</v>
+        <v>34</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C75" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D75" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E75" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F75" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H75" t="s" s="2">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="I75" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>45</v>
+        <v>35</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C76" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D76" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E76" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F76" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H76" t="s" s="2">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="I76" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>47</v>
+        <v>14</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C77" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D77" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E77" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F77" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H77" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I77" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C78" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D78" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E78" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F78" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H78" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I78" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>80</v>
+        <v>14</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C79" t="s" s="2">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D79" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E79" t="s" s="2">
-        <v>82</v>
+        <v>14</v>
       </c>
       <c r="F79" t="s" s="2">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="H79" t="s" s="2">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="I79" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>13</v>
+        <v>49</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C80" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D80" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E80" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F80" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H80" t="s" s="2">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="I80" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>30</v>
+        <v>50</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>13</v>
+        <v>85</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="C81" t="s" s="2">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="D81" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E81" t="s" s="2">
-        <v>13</v>
+        <v>87</v>
       </c>
       <c r="F81" t="s" s="2">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="H81" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I81" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J81" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>32</v>
+        <v>14</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="C82" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D82" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E82" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F82" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H82" t="s" s="2">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="I82" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J82" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="C83" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D83" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E83" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F83" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H83" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I83" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J83" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="C84" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D84" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E84" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F84" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H84" t="s" s="2">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="I84" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J84" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>13</v>
+        <v>34</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="C85" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D85" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E85" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F85" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H85" t="s" s="2">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="I85" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J85" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>45</v>
+        <v>35</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="C86" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D86" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E86" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F86" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H86" t="s" s="2">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="I86" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J86" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>47</v>
+        <v>14</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="C87" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D87" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E87" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F87" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H87" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I87" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="C88" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D88" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E88" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F88" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H88" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I88" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J88" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>83</v>
+        <v>14</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C89" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D89" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E89" t="s" s="2">
-        <v>85</v>
+        <v>14</v>
       </c>
       <c r="F89" t="s" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H89" t="s" s="2">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="I89" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J89" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>13</v>
+        <v>49</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="B90" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="B90" t="s" s="2">
-        <v>87</v>
-      </c>
       <c r="C90" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D90" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E90" t="s" s="2">
-        <v>88</v>
+        <v>14</v>
       </c>
       <c r="F90" t="s" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G90" t="s" s="2">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="H90" t="s" s="2">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="I90" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J90" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>13</v>
+        <v>50</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="B91" t="s" s="2">
         <v>89</v>
-      </c>
-      <c r="B91" t="s" s="2">
-        <v>90</v>
       </c>
       <c r="C91" t="s" s="2">
         <v>13</v>
       </c>
       <c r="D91" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E91" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F91" t="s" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G91" t="s" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H91" t="s" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I91" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J91" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="B92" t="s" s="2">
         <v>92</v>
-      </c>
-      <c r="B92" t="s" s="2">
-        <v>93</v>
       </c>
       <c r="C92" t="s" s="2">
         <v>13</v>
       </c>
       <c r="D92" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E92" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F92" t="s" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G92" t="s" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H92" t="s" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I92" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J92" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="B93" t="s" s="2">
         <v>95</v>
-      </c>
-      <c r="B93" t="s" s="2">
-        <v>96</v>
       </c>
       <c r="C93" t="s" s="2">
         <v>13</v>
       </c>
       <c r="D93" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E93" t="s" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F93" t="s" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H93" t="s" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I93" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J93" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="B94" t="s" s="2">
         <v>98</v>
       </c>
-      <c r="B94" t="s" s="2">
+      <c r="C94" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D94" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E94" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="C94" t="s" s="2">
-        <v>25</v>
-      </c>
-      <c r="D94" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="E94" t="s" s="2">
-        <v>13</v>
-      </c>
       <c r="F94" t="s" s="2">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G94" t="s" s="2">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="H94" t="s" s="2">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="I94" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J94" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>13</v>
+        <v>100</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C95" t="s" s="2">
         <v>13</v>
       </c>
       <c r="D95" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E95" t="s" s="2">
-        <v>13</v>
+        <v>102</v>
       </c>
       <c r="F95" t="s" s="2">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G95" t="s" s="2">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H95" t="s" s="2">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="I95" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J95" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>30</v>
+        <v>14</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>13</v>
+        <v>103</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="C96" t="s" s="2">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="D96" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E96" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F96" t="s" s="2">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="G96" t="s" s="2">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="H96" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I96" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J96" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>32</v>
+        <v>14</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="C97" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D97" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E97" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F97" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G97" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H97" t="s" s="2">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="I97" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J97" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="C98" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D98" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E98" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F98" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G98" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H98" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I98" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J98" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="C99" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D99" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E99" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F99" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G99" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H99" t="s" s="2">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="I99" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J99" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>13</v>
+        <v>34</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="C100" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D100" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E100" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F100" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G100" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H100" t="s" s="2">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="I100" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J100" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>45</v>
+        <v>35</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="C101" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D101" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E101" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F101" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G101" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H101" t="s" s="2">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="I101" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J101" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>47</v>
+        <v>14</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="C102" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D102" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E102" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F102" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G102" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H102" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I102" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J102" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="C103" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D103" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E103" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F103" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G103" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H103" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I103" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J103" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>100</v>
+        <v>14</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C104" t="s" s="2">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D104" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E104" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F104" t="s" s="2">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G104" t="s" s="2">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="H104" t="s" s="2">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="I104" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J104" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>13</v>
+        <v>49</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C105" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D105" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E105" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F105" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G105" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H105" t="s" s="2">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="I105" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J105" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>30</v>
+        <v>50</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>13</v>
+        <v>105</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="C106" t="s" s="2">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="D106" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E106" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F106" t="s" s="2">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="G106" t="s" s="2">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="H106" t="s" s="2">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="I106" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J106" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>32</v>
+        <v>14</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="C107" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D107" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E107" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F107" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G107" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H107" t="s" s="2">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="I107" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J107" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="C108" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D108" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E108" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F108" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G108" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H108" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I108" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J108" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>13</v>
+        <v>33</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="C109" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D109" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E109" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F109" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G109" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H109" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I109" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J109" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K109" t="s" s="2">
         <v>34</v>
@@ -4319,1752 +4334,1822 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>102</v>
+        <v>14</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="C110" t="s" s="2">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D110" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E110" t="s" s="2">
-        <v>104</v>
+        <v>14</v>
       </c>
       <c r="F110" t="s" s="2">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G110" t="s" s="2">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="H110" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I110" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J110" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="C111" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D111" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E111" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F111" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G111" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H111" t="s" s="2">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="I111" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J111" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>13</v>
+        <v>107</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="C112" t="s" s="2">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="D112" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E112" t="s" s="2">
-        <v>13</v>
+        <v>109</v>
       </c>
       <c r="F112" t="s" s="2">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="G112" t="s" s="2">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="H112" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I112" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J112" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>32</v>
+        <v>14</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="C113" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D113" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E113" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F113" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G113" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H113" t="s" s="2">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="I113" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J113" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="C114" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D114" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E114" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F114" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G114" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H114" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I114" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J114" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="C115" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D115" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E115" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F115" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G115" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H115" t="s" s="2">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="I115" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J115" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>13</v>
+        <v>34</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="C116" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D116" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E116" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F116" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G116" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H116" t="s" s="2">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="I116" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J116" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>45</v>
+        <v>35</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="C117" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D117" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E117" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F117" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G117" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H117" t="s" s="2">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="I117" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J117" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>47</v>
+        <v>14</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="C118" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D118" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E118" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F118" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G118" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H118" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I118" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J118" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="C119" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D119" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E119" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F119" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G119" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H119" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I119" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J119" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>105</v>
+        <v>14</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C120" t="s" s="2">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D120" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E120" t="s" s="2">
-        <v>107</v>
+        <v>14</v>
       </c>
       <c r="F120" t="s" s="2">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G120" t="s" s="2">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="H120" t="s" s="2">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="I120" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J120" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>13</v>
+        <v>49</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C121" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D121" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E121" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F121" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G121" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H121" t="s" s="2">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="I121" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J121" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>30</v>
+        <v>50</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>13</v>
+        <v>110</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="C122" t="s" s="2">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="D122" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E122" t="s" s="2">
-        <v>13</v>
+        <v>112</v>
       </c>
       <c r="F122" t="s" s="2">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="G122" t="s" s="2">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="H122" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I122" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J122" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>32</v>
+        <v>14</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="C123" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D123" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E123" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F123" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G123" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H123" t="s" s="2">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="I123" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J123" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="C124" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D124" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E124" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F124" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G124" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H124" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I124" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J124" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="C125" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D125" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E125" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F125" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G125" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H125" t="s" s="2">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="I125" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J125" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>13</v>
+        <v>34</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="C126" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D126" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E126" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F126" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G126" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H126" t="s" s="2">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="I126" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J126" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>45</v>
+        <v>35</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="C127" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D127" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E127" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F127" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G127" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H127" t="s" s="2">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="I127" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J127" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>47</v>
+        <v>14</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="C128" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D128" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E128" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F128" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G128" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H128" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I128" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J128" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="C129" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D129" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E129" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F129" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G129" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H129" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I129" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J129" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>108</v>
+        <v>14</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C130" t="s" s="2">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D130" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E130" t="s" s="2">
-        <v>110</v>
+        <v>14</v>
       </c>
       <c r="F130" t="s" s="2">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G130" t="s" s="2">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="H130" t="s" s="2">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="I130" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J130" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>13</v>
+        <v>49</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C131" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D131" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E131" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F131" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G131" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H131" t="s" s="2">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="I131" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J131" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>30</v>
+        <v>50</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>13</v>
+        <v>113</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="C132" t="s" s="2">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="D132" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E132" t="s" s="2">
-        <v>13</v>
+        <v>115</v>
       </c>
       <c r="F132" t="s" s="2">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="G132" t="s" s="2">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="H132" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I132" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J132" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>32</v>
+        <v>14</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="C133" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D133" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E133" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F133" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G133" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H133" t="s" s="2">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="I133" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J133" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="C134" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D134" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E134" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F134" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G134" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H134" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I134" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J134" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="C135" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D135" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E135" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F135" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G135" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H135" t="s" s="2">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="I135" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J135" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>13</v>
+        <v>34</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="C136" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D136" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E136" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F136" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G136" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H136" t="s" s="2">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="I136" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J136" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>45</v>
+        <v>35</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="C137" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D137" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E137" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F137" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G137" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H137" t="s" s="2">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="I137" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J137" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>47</v>
+        <v>14</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="C138" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D138" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E138" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F138" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G138" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H138" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I138" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J138" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="C139" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D139" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E139" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F139" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G139" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H139" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I139" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J139" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>111</v>
+        <v>14</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C140" t="s" s="2">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D140" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E140" t="s" s="2">
-        <v>113</v>
+        <v>14</v>
       </c>
       <c r="F140" t="s" s="2">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G140" t="s" s="2">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="H140" t="s" s="2">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="I140" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J140" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>13</v>
+        <v>49</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C141" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D141" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E141" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F141" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G141" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H141" t="s" s="2">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="I141" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J141" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>30</v>
+        <v>50</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>13</v>
+        <v>116</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="C142" t="s" s="2">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="D142" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E142" t="s" s="2">
-        <v>13</v>
+        <v>118</v>
       </c>
       <c r="F142" t="s" s="2">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="G142" t="s" s="2">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="H142" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I142" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J142" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>32</v>
+        <v>14</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="C143" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D143" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E143" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F143" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G143" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H143" t="s" s="2">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="I143" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J143" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="C144" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D144" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E144" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F144" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G144" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H144" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I144" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J144" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K144" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="C145" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D145" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E145" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F145" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G145" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H145" t="s" s="2">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="I145" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J145" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K145" t="s" s="2">
-        <v>13</v>
+        <v>34</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="C146" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D146" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E146" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F146" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G146" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H146" t="s" s="2">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="I146" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J146" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K146" t="s" s="2">
-        <v>45</v>
+        <v>35</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="C147" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D147" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E147" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F147" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G147" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H147" t="s" s="2">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="I147" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J147" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K147" t="s" s="2">
-        <v>47</v>
+        <v>14</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="C148" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D148" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E148" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F148" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G148" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H148" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I148" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J148" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K148" t="s" s="2">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="C149" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D149" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E149" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F149" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G149" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H149" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I149" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J149" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>114</v>
+        <v>14</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C150" t="s" s="2">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D150" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E150" t="s" s="2">
-        <v>116</v>
+        <v>14</v>
       </c>
       <c r="F150" t="s" s="2">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G150" t="s" s="2">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="H150" t="s" s="2">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="I150" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J150" t="s" s="2">
-        <v>117</v>
+        <v>14</v>
       </c>
       <c r="K150" t="s" s="2">
-        <v>13</v>
+        <v>49</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C151" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D151" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E151" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F151" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G151" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H151" t="s" s="2">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="I151" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J151" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K151" t="s" s="2">
-        <v>30</v>
+        <v>50</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>13</v>
+        <v>119</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="C152" t="s" s="2">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="D152" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E152" t="s" s="2">
-        <v>13</v>
+        <v>121</v>
       </c>
       <c r="F152" t="s" s="2">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="G152" t="s" s="2">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="H152" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I152" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J152" t="s" s="2">
-        <v>13</v>
+        <v>122</v>
       </c>
       <c r="K152" t="s" s="2">
-        <v>32</v>
+        <v>14</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="C153" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D153" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E153" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F153" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G153" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H153" t="s" s="2">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="I153" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J153" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K153" t="s" s="2">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="C154" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D154" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E154" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F154" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G154" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H154" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I154" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J154" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K154" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="C155" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D155" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E155" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F155" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G155" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H155" t="s" s="2">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="I155" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J155" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K155" t="s" s="2">
-        <v>13</v>
+        <v>34</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="C156" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D156" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E156" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F156" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G156" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H156" t="s" s="2">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="I156" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J156" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K156" t="s" s="2">
-        <v>45</v>
+        <v>35</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="C157" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D157" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E157" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F157" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G157" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H157" t="s" s="2">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="I157" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J157" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K157" t="s" s="2">
-        <v>47</v>
+        <v>14</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="C158" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D158" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E158" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F158" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G158" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H158" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I158" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J158" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K158" t="s" s="2">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="C159" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D159" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E159" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F159" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G159" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H159" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I159" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J159" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K159" t="s" s="2">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="B160" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="C160" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D160" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E160" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="F160" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="G160" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="H160" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="I160" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J160" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K160" t="s" s="2">
         <v>49</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="B161" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="C161" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D161" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E161" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="F161" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="G161" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="H161" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="I161" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J161" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K161" t="s" s="2">
+        <v>50</v>
       </c>
     </row>
   </sheetData>

--- a/output/observations-summary.xlsx
+++ b/output/observations-summary.xlsx
@@ -65,226 +65,226 @@
     <t>http://hl7.org/fhir/uv/pocd/ValueSet/11073MDC-metric (extensible)</t>
   </si>
   <si>
+    <t>dateTimeĵ, Periodĵ, Timingĵ, instantĵ</t>
+  </si>
+  <si>
+    <t>Quantityĵ, Ratioĵ</t>
+  </si>
+  <si>
+    <t>optional</t>
+  </si>
+  <si>
+    <t>t-cabs-observation-amv</t>
+  </si>
+  <si>
+    <t>T-CABS Observation AMV</t>
+  </si>
+  <si>
+    <t>null#151996</t>
+  </si>
+  <si>
+    <t>t-cabs-observation-arteriellerblutdruck</t>
+  </si>
+  <si>
+    <t>T-CABS Observation Arterial Blood Pressure</t>
+  </si>
+  <si>
+    <t>PHD Observation Categories Code System#phd-observation, PHD Observation Categories Code System#phd-observation, Observation Category Codes#vital-signs, Observation Category Codes#vital-signs</t>
+  </si>
+  <si>
+    <t>null#150016, null#85354-9</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/observation-codes (example)</t>
+  </si>
+  <si>
+    <t>dateTimeĵ, Periodĵ</t>
+  </si>
+  <si>
+    <t>CodeableConceptĵ</t>
+  </si>
+  <si>
+    <t>ISO 11073-10101 Health informatics - Point-of-care#68193</t>
+  </si>
+  <si>
+    <t>Quantityĵ</t>
+  </si>
+  <si>
+    <t>ISO 11073-10101 Health informatics - Point-of-care#67985</t>
+  </si>
+  <si>
+    <t>ISO 11073-10101 Health informatics - Point-of-care#68073</t>
+  </si>
+  <si>
+    <t>ISO 11073-10101 Health informatics - Point-of-care#67914</t>
+  </si>
+  <si>
+    <t>LOINC#8480-6</t>
+  </si>
+  <si>
+    <t>Quantity</t>
+  </si>
+  <si>
+    <t>LOINC#8462-4</t>
+  </si>
+  <si>
+    <t>LOINC#8478-0</t>
+  </si>
+  <si>
+    <t>t-cabs-observation-arteriellespo2</t>
+  </si>
+  <si>
+    <t>T-CABS Observation Arterielle SPO2</t>
+  </si>
+  <si>
+    <t>null#160300, null#2708-6</t>
+  </si>
+  <si>
+    <t>SNOMED CT#11527006</t>
+  </si>
+  <si>
+    <t>CodeableConcept</t>
+  </si>
+  <si>
+    <t>Range</t>
+  </si>
+  <si>
+    <t>ISO 11073-10101 Health informatics - Point-of-care#67892</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>ISO 11073-10101 Health informatics - Point-of-care#68104</t>
+  </si>
+  <si>
+    <t>ISO 11073-10101 Health informatics - Point-of-care#68236</t>
+  </si>
+  <si>
+    <t>ISO 11073-10101 Health informatics - Point-of-care#68232</t>
+  </si>
+  <si>
+    <t>t-cabs-observation-atemfrequenz</t>
+  </si>
+  <si>
+    <t>T-CABS Observation Respiratory Rate</t>
+  </si>
+  <si>
+    <t>null#152490, null#9279-1</t>
+  </si>
+  <si>
+    <t>t-cabs-observation-atemfrequenz-beatmet</t>
+  </si>
+  <si>
+    <t>T-CABS Observation Respiratory Rate Ventilated</t>
+  </si>
+  <si>
+    <t>null#151586</t>
+  </si>
+  <si>
+    <t>t-cabs-observation-atemzeitverhaeltnis</t>
+  </si>
+  <si>
+    <t>T-CABS Observation Respiratory Time Ratio</t>
+  </si>
+  <si>
+    <t>null#153500</t>
+  </si>
+  <si>
+    <t>t-cabs-observation-beatmungsparameter</t>
+  </si>
+  <si>
+    <t>T-CABS Observation Ventilation Parameter (abstract)</t>
+  </si>
+  <si>
+    <t>t-cabs-observation-beatmungsparametermitkomponenten</t>
+  </si>
+  <si>
+    <t>T-CABS Observation Ventilation Parameter with Components (abstract)</t>
+  </si>
+  <si>
+    <t>t-cabs-observation-bmi</t>
+  </si>
+  <si>
+    <t>T-CABS Observation BMI</t>
+  </si>
+  <si>
+    <t>null#188752, null#39156-5</t>
+  </si>
+  <si>
+    <t>t-cabs-observation-druck-minmax</t>
+  </si>
+  <si>
+    <t>T-CABS Observation Pressure MIN/MAX</t>
+  </si>
+  <si>
+    <t>null#151792</t>
+  </si>
+  <si>
+    <t>Periodĵ, dateTime</t>
+  </si>
+  <si>
+    <t>ISO 11073-10101 Health informatics - Point-of-care#151794</t>
+  </si>
+  <si>
+    <t>ISO 11073-10101 Health informatics - Point-of-care#151793</t>
+  </si>
+  <si>
+    <t>t-cabs-observation-gehstrecke</t>
+  </si>
+  <si>
+    <t>T-CABS Observation Walking Distance</t>
+  </si>
+  <si>
+    <t>null#8454247, null#41950-7</t>
+  </si>
+  <si>
+    <t>t-cabs-observation-herzfrequenz</t>
+  </si>
+  <si>
+    <t>T-CABS Observation Heart Rate</t>
+  </si>
+  <si>
+    <t>null#147842, null#8867-4</t>
+  </si>
+  <si>
+    <t>t-cabs-observation-ipap</t>
+  </si>
+  <si>
+    <t>T-CABS Observation IPAP</t>
+  </si>
+  <si>
+    <t>null#8410976</t>
+  </si>
+  <si>
+    <t>t-cabs-observation-koerpergewicht</t>
+  </si>
+  <si>
+    <t>T-CABS Observation Body Weight</t>
+  </si>
+  <si>
+    <t>null#188736, null#29463-7</t>
+  </si>
+  <si>
+    <t>t-cabs-observation-koerpertemperatur</t>
+  </si>
+  <si>
+    <t>T-CABS Observation Body Temperature</t>
+  </si>
+  <si>
+    <t>null#150364, null#8310-5</t>
+  </si>
+  <si>
+    <t>t-cabs-observation-leckage</t>
+  </si>
+  <si>
+    <t>T-CABS Observation Leakage</t>
+  </si>
+  <si>
+    <t>null#152432</t>
+  </si>
+  <si>
     <t>Periodĵ, dateTime, instant</t>
-  </si>
-  <si>
-    <t>Quantityĵ, Ratioĵ</t>
-  </si>
-  <si>
-    <t>optional</t>
-  </si>
-  <si>
-    <t>t-cabs-observation-amv</t>
-  </si>
-  <si>
-    <t>T-CABS Observation AMV</t>
-  </si>
-  <si>
-    <t>null#151996</t>
-  </si>
-  <si>
-    <t>dateTimeĵ, Periodĵ, Timingĵ, instantĵ</t>
-  </si>
-  <si>
-    <t>t-cabs-observation-arteriellerblutdruck</t>
-  </si>
-  <si>
-    <t>T-CABS Observation Arterial Blood Pressure</t>
-  </si>
-  <si>
-    <t>PHD Observation Categories Code System#phd-observation, PHD Observation Categories Code System#phd-observation, Observation Category Codes#vital-signs, Observation Category Codes#vital-signs</t>
-  </si>
-  <si>
-    <t>null#150016, null#85354-9</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-codes (example)</t>
-  </si>
-  <si>
-    <t>dateTimeĵ, Periodĵ</t>
-  </si>
-  <si>
-    <t>CodeableConceptĵ</t>
-  </si>
-  <si>
-    <t>ISO 11073-10101 Health informatics - Point-of-care#68193</t>
-  </si>
-  <si>
-    <t>Quantityĵ</t>
-  </si>
-  <si>
-    <t>ISO 11073-10101 Health informatics - Point-of-care#67985</t>
-  </si>
-  <si>
-    <t>ISO 11073-10101 Health informatics - Point-of-care#68073</t>
-  </si>
-  <si>
-    <t>ISO 11073-10101 Health informatics - Point-of-care#67914</t>
-  </si>
-  <si>
-    <t>LOINC#8480-6</t>
-  </si>
-  <si>
-    <t>Quantity</t>
-  </si>
-  <si>
-    <t>LOINC#8462-4</t>
-  </si>
-  <si>
-    <t>LOINC#8478-0</t>
-  </si>
-  <si>
-    <t>t-cabs-observation-arteriellespo2</t>
-  </si>
-  <si>
-    <t>T-CABS Observation SPO2</t>
-  </si>
-  <si>
-    <t>null#160300, null#2708-6</t>
-  </si>
-  <si>
-    <t>SNOMED CT#11527006</t>
-  </si>
-  <si>
-    <t>CodeableConcept</t>
-  </si>
-  <si>
-    <t>Range</t>
-  </si>
-  <si>
-    <t>ISO 11073-10101 Health informatics - Point-of-care#67892</t>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>ISO 11073-10101 Health informatics - Point-of-care#68104</t>
-  </si>
-  <si>
-    <t>ISO 11073-10101 Health informatics - Point-of-care#68236</t>
-  </si>
-  <si>
-    <t>ISO 11073-10101 Health informatics - Point-of-care#68232</t>
-  </si>
-  <si>
-    <t>t-cabs-observation-atemfrequenz</t>
-  </si>
-  <si>
-    <t>T-CABS Observation Respiratory Rate</t>
-  </si>
-  <si>
-    <t>null#152490, null#9279-1</t>
-  </si>
-  <si>
-    <t>t-cabs-observation-atemfrequenz-beatmet</t>
-  </si>
-  <si>
-    <t>T-CABS Observation Respiratory Rate Ventilated</t>
-  </si>
-  <si>
-    <t>null#151586</t>
-  </si>
-  <si>
-    <t>t-cabs-observation-atemzeitverhaeltnis</t>
-  </si>
-  <si>
-    <t>T-CABS Observation Respiratory Time Ratio</t>
-  </si>
-  <si>
-    <t>null#153500</t>
-  </si>
-  <si>
-    <t>t-cabs-observation-beatmungsparameter</t>
-  </si>
-  <si>
-    <t>T-CABS Observation Ventilation Parameter (abstract)</t>
-  </si>
-  <si>
-    <t>t-cabs-observation-beatmungsparametermitkomponenten</t>
-  </si>
-  <si>
-    <t>T-CABS Observation Ventilation Parameter with Components (abstract)</t>
-  </si>
-  <si>
-    <t>t-cabs-observation-bmi</t>
-  </si>
-  <si>
-    <t>T-CABS Observation BMI</t>
-  </si>
-  <si>
-    <t>null#188752, null#39156-5</t>
-  </si>
-  <si>
-    <t>t-cabs-observation-druck-minmax</t>
-  </si>
-  <si>
-    <t>T-CABS Observation Pressure MIN/MAX</t>
-  </si>
-  <si>
-    <t>null#151792</t>
-  </si>
-  <si>
-    <t>Periodĵ, dateTime</t>
-  </si>
-  <si>
-    <t>ISO 11073-10101 Health informatics - Point-of-care#151794</t>
-  </si>
-  <si>
-    <t>ISO 11073-10101 Health informatics - Point-of-care#151793</t>
-  </si>
-  <si>
-    <t>t-cabs-observation-gehstrecke</t>
-  </si>
-  <si>
-    <t>T-CABS Observation Walking Distance</t>
-  </si>
-  <si>
-    <t>null#158033, null#41950-7</t>
-  </si>
-  <si>
-    <t>t-cabs-observation-herzfrequenz</t>
-  </si>
-  <si>
-    <t>T-CABS Observation Heart Rate</t>
-  </si>
-  <si>
-    <t>null#147842, null#8867-4</t>
-  </si>
-  <si>
-    <t>t-cabs-observation-ipap</t>
-  </si>
-  <si>
-    <t>T-CABS Observation IPAP</t>
-  </si>
-  <si>
-    <t>null#8410976</t>
-  </si>
-  <si>
-    <t>t-cabs-observation-koerpergewicht</t>
-  </si>
-  <si>
-    <t>T-CABS Observation Body Weight</t>
-  </si>
-  <si>
-    <t>null#188800, null#29463-7</t>
-  </si>
-  <si>
-    <t>t-cabs-observation-koerpertemperatur</t>
-  </si>
-  <si>
-    <t>T-CABS Observation Body Temperature</t>
-  </si>
-  <si>
-    <t>null#150364, null#8310-5</t>
-  </si>
-  <si>
-    <t>t-cabs-observation-leckage</t>
-  </si>
-  <si>
-    <t>T-CABS Observation Leakage</t>
-  </si>
-  <si>
-    <t>null#152432</t>
   </si>
   <si>
     <t>t-cabs-observation-peep</t>
@@ -607,7 +607,7 @@
         <v>16</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="H3" t="s" s="2">
         <v>18</v>
@@ -624,25 +624,25 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="B4" t="s" s="2">
         <v>24</v>
       </c>
-      <c r="B4" t="s" s="2">
+      <c r="C4" t="s" s="2">
         <v>25</v>
       </c>
-      <c r="C4" t="s" s="2">
+      <c r="D4" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E4" t="s" s="2">
         <v>26</v>
       </c>
-      <c r="D4" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E4" t="s" s="2">
+      <c r="F4" t="s" s="2">
         <v>27</v>
       </c>
-      <c r="F4" t="s" s="2">
+      <c r="G4" t="s" s="2">
         <v>28</v>
-      </c>
-      <c r="G4" t="s" s="2">
-        <v>29</v>
       </c>
       <c r="H4" t="s" s="2">
         <v>14</v>
@@ -662,7 +662,7 @@
         <v>14</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C5" t="s" s="2">
         <v>14</v>
@@ -680,16 +680,16 @@
         <v>14</v>
       </c>
       <c r="H5" t="s" s="2">
+        <v>29</v>
+      </c>
+      <c r="I5" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J5" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K5" t="s" s="2">
         <v>30</v>
-      </c>
-      <c r="I5" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="J5" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="K5" t="s" s="2">
-        <v>31</v>
       </c>
     </row>
     <row r="6">
@@ -697,7 +697,7 @@
         <v>14</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C6" t="s" s="2">
         <v>14</v>
@@ -715,16 +715,16 @@
         <v>14</v>
       </c>
       <c r="H6" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="I6" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J6" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K6" t="s" s="2">
         <v>32</v>
-      </c>
-      <c r="I6" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="J6" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="K6" t="s" s="2">
-        <v>33</v>
       </c>
     </row>
     <row r="7">
@@ -732,7 +732,7 @@
         <v>14</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C7" t="s" s="2">
         <v>14</v>
@@ -750,7 +750,7 @@
         <v>14</v>
       </c>
       <c r="H7" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I7" t="s" s="2">
         <v>19</v>
@@ -759,7 +759,7 @@
         <v>14</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8">
@@ -767,7 +767,7 @@
         <v>14</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C8" t="s" s="2">
         <v>14</v>
@@ -785,7 +785,7 @@
         <v>14</v>
       </c>
       <c r="H8" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I8" t="s" s="2">
         <v>19</v>
@@ -802,7 +802,7 @@
         <v>14</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C9" t="s" s="2">
         <v>14</v>
@@ -820,7 +820,7 @@
         <v>14</v>
       </c>
       <c r="H9" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I9" t="s" s="2">
         <v>19</v>
@@ -829,7 +829,7 @@
         <v>14</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10">
@@ -837,7 +837,7 @@
         <v>14</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C10" t="s" s="2">
         <v>14</v>
@@ -846,16 +846,16 @@
         <v>14</v>
       </c>
       <c r="E10" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="F10" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="G10" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="H10" t="s" s="2">
         <v>36</v>
-      </c>
-      <c r="F10" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="G10" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="H10" t="s" s="2">
-        <v>37</v>
       </c>
       <c r="I10" t="s" s="2">
         <v>19</v>
@@ -872,7 +872,7 @@
         <v>14</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C11" t="s" s="2">
         <v>14</v>
@@ -881,7 +881,7 @@
         <v>14</v>
       </c>
       <c r="E11" t="s" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F11" t="s" s="2">
         <v>14</v>
@@ -890,7 +890,7 @@
         <v>14</v>
       </c>
       <c r="H11" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I11" t="s" s="2">
         <v>19</v>
@@ -907,7 +907,7 @@
         <v>14</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C12" t="s" s="2">
         <v>14</v>
@@ -916,7 +916,7 @@
         <v>14</v>
       </c>
       <c r="E12" t="s" s="2">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F12" t="s" s="2">
         <v>14</v>
@@ -925,7 +925,7 @@
         <v>14</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I12" t="s" s="2">
         <v>19</v>
@@ -939,34 +939,34 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="B13" t="s" s="2">
         <v>40</v>
       </c>
-      <c r="B13" t="s" s="2">
+      <c r="C13" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="D13" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E13" t="s" s="2">
         <v>41</v>
       </c>
-      <c r="C13" t="s" s="2">
-        <v>26</v>
-      </c>
-      <c r="D13" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E13" t="s" s="2">
+      <c r="F13" t="s" s="2">
+        <v>27</v>
+      </c>
+      <c r="G13" t="s" s="2">
+        <v>28</v>
+      </c>
+      <c r="H13" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="I13" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J13" t="s" s="2">
         <v>42</v>
-      </c>
-      <c r="F13" t="s" s="2">
-        <v>28</v>
-      </c>
-      <c r="G13" t="s" s="2">
-        <v>29</v>
-      </c>
-      <c r="H13" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="I13" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="J13" t="s" s="2">
-        <v>43</v>
       </c>
       <c r="K13" t="s" s="2">
         <v>14</v>
@@ -977,7 +977,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C14" t="s" s="2">
         <v>14</v>
@@ -995,7 +995,7 @@
         <v>14</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I14" t="s" s="2">
         <v>19</v>
@@ -1004,7 +1004,7 @@
         <v>14</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="15">
@@ -1012,7 +1012,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C15" t="s" s="2">
         <v>14</v>
@@ -1030,7 +1030,7 @@
         <v>14</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I15" t="s" s="2">
         <v>19</v>
@@ -1039,7 +1039,7 @@
         <v>14</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="16">
@@ -1047,7 +1047,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C16" t="s" s="2">
         <v>14</v>
@@ -1065,7 +1065,7 @@
         <v>14</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I16" t="s" s="2">
         <v>19</v>
@@ -1074,7 +1074,7 @@
         <v>14</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="17">
@@ -1082,7 +1082,7 @@
         <v>14</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C17" t="s" s="2">
         <v>14</v>
@@ -1100,7 +1100,7 @@
         <v>14</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I17" t="s" s="2">
         <v>19</v>
@@ -1109,7 +1109,7 @@
         <v>14</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="18">
@@ -1117,7 +1117,7 @@
         <v>14</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C18" t="s" s="2">
         <v>14</v>
@@ -1135,7 +1135,7 @@
         <v>14</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>19</v>
@@ -1152,7 +1152,7 @@
         <v>14</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C19" t="s" s="2">
         <v>14</v>
@@ -1170,16 +1170,16 @@
         <v>14</v>
       </c>
       <c r="H19" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="I19" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J19" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K19" t="s" s="2">
         <v>45</v>
-      </c>
-      <c r="I19" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="J19" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="K19" t="s" s="2">
-        <v>46</v>
       </c>
     </row>
     <row r="20">
@@ -1187,7 +1187,7 @@
         <v>14</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C20" t="s" s="2">
         <v>14</v>
@@ -1205,16 +1205,16 @@
         <v>14</v>
       </c>
       <c r="H20" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="I20" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J20" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K20" t="s" s="2">
         <v>47</v>
-      </c>
-      <c r="I20" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="J20" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="K20" t="s" s="2">
-        <v>48</v>
       </c>
     </row>
     <row r="21">
@@ -1222,7 +1222,7 @@
         <v>14</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C21" t="s" s="2">
         <v>14</v>
@@ -1240,7 +1240,7 @@
         <v>14</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I21" t="s" s="2">
         <v>19</v>
@@ -1249,7 +1249,7 @@
         <v>14</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="22">
@@ -1257,7 +1257,7 @@
         <v>14</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C22" t="s" s="2">
         <v>14</v>
@@ -1275,7 +1275,7 @@
         <v>14</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I22" t="s" s="2">
         <v>19</v>
@@ -1284,33 +1284,33 @@
         <v>14</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="B23" t="s" s="2">
         <v>51</v>
       </c>
-      <c r="B23" t="s" s="2">
+      <c r="C23" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="D23" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E23" t="s" s="2">
         <v>52</v>
       </c>
-      <c r="C23" t="s" s="2">
-        <v>26</v>
-      </c>
-      <c r="D23" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E23" t="s" s="2">
-        <v>53</v>
-      </c>
       <c r="F23" t="s" s="2">
+        <v>27</v>
+      </c>
+      <c r="G23" t="s" s="2">
         <v>28</v>
       </c>
-      <c r="G23" t="s" s="2">
-        <v>29</v>
-      </c>
       <c r="H23" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>19</v>
@@ -1327,7 +1327,7 @@
         <v>14</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C24" t="s" s="2">
         <v>14</v>
@@ -1345,7 +1345,7 @@
         <v>14</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>19</v>
@@ -1354,7 +1354,7 @@
         <v>14</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="25">
@@ -1362,7 +1362,7 @@
         <v>14</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C25" t="s" s="2">
         <v>14</v>
@@ -1380,7 +1380,7 @@
         <v>14</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>19</v>
@@ -1389,7 +1389,7 @@
         <v>14</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="26">
@@ -1397,7 +1397,7 @@
         <v>14</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C26" t="s" s="2">
         <v>14</v>
@@ -1415,7 +1415,7 @@
         <v>14</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>19</v>
@@ -1424,7 +1424,7 @@
         <v>14</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="27">
@@ -1432,7 +1432,7 @@
         <v>14</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C27" t="s" s="2">
         <v>14</v>
@@ -1450,7 +1450,7 @@
         <v>14</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>19</v>
@@ -1459,7 +1459,7 @@
         <v>14</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="28">
@@ -1467,7 +1467,7 @@
         <v>14</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C28" t="s" s="2">
         <v>14</v>
@@ -1485,7 +1485,7 @@
         <v>14</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>19</v>
@@ -1502,7 +1502,7 @@
         <v>14</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C29" t="s" s="2">
         <v>14</v>
@@ -1520,16 +1520,16 @@
         <v>14</v>
       </c>
       <c r="H29" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="I29" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J29" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K29" t="s" s="2">
         <v>45</v>
-      </c>
-      <c r="I29" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="J29" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="K29" t="s" s="2">
-        <v>46</v>
       </c>
     </row>
     <row r="30">
@@ -1537,7 +1537,7 @@
         <v>14</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C30" t="s" s="2">
         <v>14</v>
@@ -1555,16 +1555,16 @@
         <v>14</v>
       </c>
       <c r="H30" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="I30" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J30" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K30" t="s" s="2">
         <v>47</v>
-      </c>
-      <c r="I30" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="J30" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="K30" t="s" s="2">
-        <v>48</v>
       </c>
     </row>
     <row r="31">
@@ -1572,7 +1572,7 @@
         <v>14</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C31" t="s" s="2">
         <v>14</v>
@@ -1590,7 +1590,7 @@
         <v>14</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>19</v>
@@ -1599,7 +1599,7 @@
         <v>14</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="32">
@@ -1607,7 +1607,7 @@
         <v>14</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C32" t="s" s="2">
         <v>14</v>
@@ -1625,7 +1625,7 @@
         <v>14</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>19</v>
@@ -1634,15 +1634,15 @@
         <v>14</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
+        <v>53</v>
+      </c>
+      <c r="B33" t="s" s="2">
         <v>54</v>
-      </c>
-      <c r="B33" t="s" s="2">
-        <v>55</v>
       </c>
       <c r="C33" t="s" s="2">
         <v>13</v>
@@ -1651,13 +1651,13 @@
         <v>14</v>
       </c>
       <c r="E33" t="s" s="2">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F33" t="s" s="2">
         <v>16</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>18</v>
@@ -1674,10 +1674,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="B34" t="s" s="2">
         <v>57</v>
-      </c>
-      <c r="B34" t="s" s="2">
-        <v>58</v>
       </c>
       <c r="C34" t="s" s="2">
         <v>13</v>
@@ -1686,13 +1686,13 @@
         <v>14</v>
       </c>
       <c r="E34" t="s" s="2">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F34" t="s" s="2">
         <v>16</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>18</v>
@@ -1709,10 +1709,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="B35" t="s" s="2">
         <v>60</v>
-      </c>
-      <c r="B35" t="s" s="2">
-        <v>61</v>
       </c>
       <c r="C35" t="s" s="2">
         <v>13</v>
@@ -1727,7 +1727,7 @@
         <v>16</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>18</v>
@@ -1744,10 +1744,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="B36" t="s" s="2">
         <v>62</v>
-      </c>
-      <c r="B36" t="s" s="2">
-        <v>63</v>
       </c>
       <c r="C36" t="s" s="2">
         <v>13</v>
@@ -1762,7 +1762,7 @@
         <v>16</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>14</v>
@@ -1779,28 +1779,28 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="B37" t="s" s="2">
         <v>64</v>
       </c>
-      <c r="B37" t="s" s="2">
+      <c r="C37" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="D37" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E37" t="s" s="2">
         <v>65</v>
       </c>
-      <c r="C37" t="s" s="2">
-        <v>26</v>
-      </c>
-      <c r="D37" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E37" t="s" s="2">
-        <v>66</v>
-      </c>
       <c r="F37" t="s" s="2">
+        <v>27</v>
+      </c>
+      <c r="G37" t="s" s="2">
         <v>28</v>
       </c>
-      <c r="G37" t="s" s="2">
-        <v>29</v>
-      </c>
       <c r="H37" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>19</v>
@@ -1817,7 +1817,7 @@
         <v>14</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C38" t="s" s="2">
         <v>14</v>
@@ -1835,7 +1835,7 @@
         <v>14</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>19</v>
@@ -1844,7 +1844,7 @@
         <v>14</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="39">
@@ -1852,7 +1852,7 @@
         <v>14</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C39" t="s" s="2">
         <v>14</v>
@@ -1870,7 +1870,7 @@
         <v>14</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>19</v>
@@ -1879,7 +1879,7 @@
         <v>14</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="40">
@@ -1887,7 +1887,7 @@
         <v>14</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C40" t="s" s="2">
         <v>14</v>
@@ -1905,7 +1905,7 @@
         <v>14</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>19</v>
@@ -1914,7 +1914,7 @@
         <v>14</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="41">
@@ -1922,7 +1922,7 @@
         <v>14</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C41" t="s" s="2">
         <v>14</v>
@@ -1940,7 +1940,7 @@
         <v>14</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>19</v>
@@ -1949,7 +1949,7 @@
         <v>14</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="42">
@@ -1957,7 +1957,7 @@
         <v>14</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C42" t="s" s="2">
         <v>14</v>
@@ -1975,7 +1975,7 @@
         <v>14</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>19</v>
@@ -1992,7 +1992,7 @@
         <v>14</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C43" t="s" s="2">
         <v>14</v>
@@ -2010,16 +2010,16 @@
         <v>14</v>
       </c>
       <c r="H43" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="I43" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J43" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K43" t="s" s="2">
         <v>45</v>
-      </c>
-      <c r="I43" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="J43" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="K43" t="s" s="2">
-        <v>46</v>
       </c>
     </row>
     <row r="44">
@@ -2027,7 +2027,7 @@
         <v>14</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C44" t="s" s="2">
         <v>14</v>
@@ -2045,16 +2045,16 @@
         <v>14</v>
       </c>
       <c r="H44" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="I44" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J44" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K44" t="s" s="2">
         <v>47</v>
-      </c>
-      <c r="I44" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="J44" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="K44" t="s" s="2">
-        <v>48</v>
       </c>
     </row>
     <row r="45">
@@ -2062,7 +2062,7 @@
         <v>14</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C45" t="s" s="2">
         <v>14</v>
@@ -2080,7 +2080,7 @@
         <v>14</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I45" t="s" s="2">
         <v>19</v>
@@ -2089,7 +2089,7 @@
         <v>14</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="46">
@@ -2097,7 +2097,7 @@
         <v>14</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C46" t="s" s="2">
         <v>14</v>
@@ -2115,7 +2115,7 @@
         <v>14</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>19</v>
@@ -2124,15 +2124,15 @@
         <v>14</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
+        <v>66</v>
+      </c>
+      <c r="B47" t="s" s="2">
         <v>67</v>
-      </c>
-      <c r="B47" t="s" s="2">
-        <v>68</v>
       </c>
       <c r="C47" t="s" s="2">
         <v>13</v>
@@ -2141,13 +2141,13 @@
         <v>14</v>
       </c>
       <c r="E47" t="s" s="2">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F47" t="s" s="2">
         <v>16</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>14</v>
@@ -2167,7 +2167,7 @@
         <v>14</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C48" t="s" s="2">
         <v>14</v>
@@ -2176,7 +2176,7 @@
         <v>14</v>
       </c>
       <c r="E48" t="s" s="2">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F48" t="s" s="2">
         <v>14</v>
@@ -2185,7 +2185,7 @@
         <v>14</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>19</v>
@@ -2202,7 +2202,7 @@
         <v>14</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C49" t="s" s="2">
         <v>14</v>
@@ -2211,7 +2211,7 @@
         <v>14</v>
       </c>
       <c r="E49" t="s" s="2">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F49" t="s" s="2">
         <v>14</v>
@@ -2220,7 +2220,7 @@
         <v>14</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>19</v>
@@ -2234,28 +2234,28 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="B50" t="s" s="2">
         <v>73</v>
       </c>
-      <c r="B50" t="s" s="2">
+      <c r="C50" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="D50" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E50" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="C50" t="s" s="2">
-        <v>26</v>
-      </c>
-      <c r="D50" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E50" t="s" s="2">
-        <v>75</v>
-      </c>
       <c r="F50" t="s" s="2">
+        <v>27</v>
+      </c>
+      <c r="G50" t="s" s="2">
         <v>28</v>
       </c>
-      <c r="G50" t="s" s="2">
-        <v>29</v>
-      </c>
       <c r="H50" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>19</v>
@@ -2272,7 +2272,7 @@
         <v>14</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C51" t="s" s="2">
         <v>14</v>
@@ -2290,7 +2290,7 @@
         <v>14</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>19</v>
@@ -2299,7 +2299,7 @@
         <v>14</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="52">
@@ -2307,7 +2307,7 @@
         <v>14</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C52" t="s" s="2">
         <v>14</v>
@@ -2325,7 +2325,7 @@
         <v>14</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>19</v>
@@ -2334,7 +2334,7 @@
         <v>14</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="53">
@@ -2342,7 +2342,7 @@
         <v>14</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C53" t="s" s="2">
         <v>14</v>
@@ -2360,7 +2360,7 @@
         <v>14</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>19</v>
@@ -2369,7 +2369,7 @@
         <v>14</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="54">
@@ -2377,7 +2377,7 @@
         <v>14</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C54" t="s" s="2">
         <v>14</v>
@@ -2395,7 +2395,7 @@
         <v>14</v>
       </c>
       <c r="H54" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I54" t="s" s="2">
         <v>19</v>
@@ -2404,7 +2404,7 @@
         <v>14</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="55">
@@ -2412,7 +2412,7 @@
         <v>14</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C55" t="s" s="2">
         <v>14</v>
@@ -2430,7 +2430,7 @@
         <v>14</v>
       </c>
       <c r="H55" t="s" s="2">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I55" t="s" s="2">
         <v>19</v>
@@ -2447,7 +2447,7 @@
         <v>14</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C56" t="s" s="2">
         <v>14</v>
@@ -2465,16 +2465,16 @@
         <v>14</v>
       </c>
       <c r="H56" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="I56" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J56" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K56" t="s" s="2">
         <v>45</v>
-      </c>
-      <c r="I56" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="J56" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="K56" t="s" s="2">
-        <v>46</v>
       </c>
     </row>
     <row r="57">
@@ -2482,7 +2482,7 @@
         <v>14</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C57" t="s" s="2">
         <v>14</v>
@@ -2500,16 +2500,16 @@
         <v>14</v>
       </c>
       <c r="H57" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="I57" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J57" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K57" t="s" s="2">
         <v>47</v>
-      </c>
-      <c r="I57" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="J57" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="K57" t="s" s="2">
-        <v>48</v>
       </c>
     </row>
     <row r="58">
@@ -2517,7 +2517,7 @@
         <v>14</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C58" t="s" s="2">
         <v>14</v>
@@ -2535,7 +2535,7 @@
         <v>14</v>
       </c>
       <c r="H58" t="s" s="2">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I58" t="s" s="2">
         <v>19</v>
@@ -2544,7 +2544,7 @@
         <v>14</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="59">
@@ -2552,7 +2552,7 @@
         <v>14</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C59" t="s" s="2">
         <v>14</v>
@@ -2570,7 +2570,7 @@
         <v>14</v>
       </c>
       <c r="H59" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I59" t="s" s="2">
         <v>19</v>
@@ -2579,33 +2579,33 @@
         <v>14</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="B60" t="s" s="2">
         <v>76</v>
       </c>
-      <c r="B60" t="s" s="2">
+      <c r="C60" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="D60" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E60" t="s" s="2">
         <v>77</v>
       </c>
-      <c r="C60" t="s" s="2">
-        <v>26</v>
-      </c>
-      <c r="D60" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E60" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="F60" t="s" s="2">
+        <v>27</v>
+      </c>
+      <c r="G60" t="s" s="2">
         <v>28</v>
       </c>
-      <c r="G60" t="s" s="2">
-        <v>29</v>
-      </c>
       <c r="H60" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I60" t="s" s="2">
         <v>19</v>
@@ -2622,7 +2622,7 @@
         <v>14</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C61" t="s" s="2">
         <v>14</v>
@@ -2640,7 +2640,7 @@
         <v>14</v>
       </c>
       <c r="H61" t="s" s="2">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I61" t="s" s="2">
         <v>19</v>
@@ -2649,7 +2649,7 @@
         <v>14</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="62">
@@ -2657,7 +2657,7 @@
         <v>14</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C62" t="s" s="2">
         <v>14</v>
@@ -2675,7 +2675,7 @@
         <v>14</v>
       </c>
       <c r="H62" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I62" t="s" s="2">
         <v>19</v>
@@ -2684,7 +2684,7 @@
         <v>14</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="63">
@@ -2692,7 +2692,7 @@
         <v>14</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C63" t="s" s="2">
         <v>14</v>
@@ -2710,7 +2710,7 @@
         <v>14</v>
       </c>
       <c r="H63" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I63" t="s" s="2">
         <v>19</v>
@@ -2719,7 +2719,7 @@
         <v>14</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="64">
@@ -2727,7 +2727,7 @@
         <v>14</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C64" t="s" s="2">
         <v>14</v>
@@ -2745,7 +2745,7 @@
         <v>14</v>
       </c>
       <c r="H64" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I64" t="s" s="2">
         <v>19</v>
@@ -2754,7 +2754,7 @@
         <v>14</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="65">
@@ -2762,7 +2762,7 @@
         <v>14</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C65" t="s" s="2">
         <v>14</v>
@@ -2780,7 +2780,7 @@
         <v>14</v>
       </c>
       <c r="H65" t="s" s="2">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I65" t="s" s="2">
         <v>19</v>
@@ -2797,7 +2797,7 @@
         <v>14</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C66" t="s" s="2">
         <v>14</v>
@@ -2815,16 +2815,16 @@
         <v>14</v>
       </c>
       <c r="H66" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="I66" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J66" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K66" t="s" s="2">
         <v>45</v>
-      </c>
-      <c r="I66" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="J66" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="K66" t="s" s="2">
-        <v>46</v>
       </c>
     </row>
     <row r="67">
@@ -2832,7 +2832,7 @@
         <v>14</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C67" t="s" s="2">
         <v>14</v>
@@ -2850,16 +2850,16 @@
         <v>14</v>
       </c>
       <c r="H67" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="I67" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J67" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K67" t="s" s="2">
         <v>47</v>
-      </c>
-      <c r="I67" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="J67" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="K67" t="s" s="2">
-        <v>48</v>
       </c>
     </row>
     <row r="68">
@@ -2867,7 +2867,7 @@
         <v>14</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C68" t="s" s="2">
         <v>14</v>
@@ -2885,7 +2885,7 @@
         <v>14</v>
       </c>
       <c r="H68" t="s" s="2">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I68" t="s" s="2">
         <v>19</v>
@@ -2894,7 +2894,7 @@
         <v>14</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="69">
@@ -2902,7 +2902,7 @@
         <v>14</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C69" t="s" s="2">
         <v>14</v>
@@ -2920,7 +2920,7 @@
         <v>14</v>
       </c>
       <c r="H69" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I69" t="s" s="2">
         <v>19</v>
@@ -2929,15 +2929,15 @@
         <v>14</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="B70" t="s" s="2">
         <v>79</v>
-      </c>
-      <c r="B70" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="C70" t="s" s="2">
         <v>13</v>
@@ -2946,13 +2946,13 @@
         <v>14</v>
       </c>
       <c r="E70" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F70" t="s" s="2">
         <v>16</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>18</v>
@@ -2969,28 +2969,28 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="B71" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="B71" t="s" s="2">
+      <c r="C71" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="D71" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E71" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="C71" t="s" s="2">
-        <v>26</v>
-      </c>
-      <c r="D71" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E71" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="F71" t="s" s="2">
+        <v>27</v>
+      </c>
+      <c r="G71" t="s" s="2">
         <v>28</v>
       </c>
-      <c r="G71" t="s" s="2">
-        <v>29</v>
-      </c>
       <c r="H71" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I71" t="s" s="2">
         <v>19</v>
@@ -3007,7 +3007,7 @@
         <v>14</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C72" t="s" s="2">
         <v>14</v>
@@ -3025,7 +3025,7 @@
         <v>14</v>
       </c>
       <c r="H72" t="s" s="2">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I72" t="s" s="2">
         <v>19</v>
@@ -3034,7 +3034,7 @@
         <v>14</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="73">
@@ -3042,7 +3042,7 @@
         <v>14</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C73" t="s" s="2">
         <v>14</v>
@@ -3060,7 +3060,7 @@
         <v>14</v>
       </c>
       <c r="H73" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I73" t="s" s="2">
         <v>19</v>
@@ -3069,7 +3069,7 @@
         <v>14</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="74">
@@ -3077,7 +3077,7 @@
         <v>14</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C74" t="s" s="2">
         <v>14</v>
@@ -3095,7 +3095,7 @@
         <v>14</v>
       </c>
       <c r="H74" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I74" t="s" s="2">
         <v>19</v>
@@ -3104,7 +3104,7 @@
         <v>14</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="75">
@@ -3112,7 +3112,7 @@
         <v>14</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C75" t="s" s="2">
         <v>14</v>
@@ -3130,7 +3130,7 @@
         <v>14</v>
       </c>
       <c r="H75" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I75" t="s" s="2">
         <v>19</v>
@@ -3139,7 +3139,7 @@
         <v>14</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="76">
@@ -3147,7 +3147,7 @@
         <v>14</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C76" t="s" s="2">
         <v>14</v>
@@ -3165,7 +3165,7 @@
         <v>14</v>
       </c>
       <c r="H76" t="s" s="2">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I76" t="s" s="2">
         <v>19</v>
@@ -3182,7 +3182,7 @@
         <v>14</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C77" t="s" s="2">
         <v>14</v>
@@ -3200,16 +3200,16 @@
         <v>14</v>
       </c>
       <c r="H77" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="I77" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J77" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K77" t="s" s="2">
         <v>45</v>
-      </c>
-      <c r="I77" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="J77" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="K77" t="s" s="2">
-        <v>46</v>
       </c>
     </row>
     <row r="78">
@@ -3217,7 +3217,7 @@
         <v>14</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C78" t="s" s="2">
         <v>14</v>
@@ -3235,16 +3235,16 @@
         <v>14</v>
       </c>
       <c r="H78" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="I78" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J78" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K78" t="s" s="2">
         <v>47</v>
-      </c>
-      <c r="I78" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="J78" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="K78" t="s" s="2">
-        <v>48</v>
       </c>
     </row>
     <row r="79">
@@ -3252,7 +3252,7 @@
         <v>14</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C79" t="s" s="2">
         <v>14</v>
@@ -3270,7 +3270,7 @@
         <v>14</v>
       </c>
       <c r="H79" t="s" s="2">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I79" t="s" s="2">
         <v>19</v>
@@ -3279,7 +3279,7 @@
         <v>14</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="80">
@@ -3287,7 +3287,7 @@
         <v>14</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C80" t="s" s="2">
         <v>14</v>
@@ -3305,7 +3305,7 @@
         <v>14</v>
       </c>
       <c r="H80" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I80" t="s" s="2">
         <v>19</v>
@@ -3314,33 +3314,33 @@
         <v>14</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="B81" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="B81" t="s" s="2">
+      <c r="C81" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="D81" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E81" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="C81" t="s" s="2">
-        <v>26</v>
-      </c>
-      <c r="D81" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E81" t="s" s="2">
-        <v>87</v>
-      </c>
       <c r="F81" t="s" s="2">
+        <v>27</v>
+      </c>
+      <c r="G81" t="s" s="2">
         <v>28</v>
       </c>
-      <c r="G81" t="s" s="2">
-        <v>29</v>
-      </c>
       <c r="H81" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I81" t="s" s="2">
         <v>19</v>
@@ -3357,7 +3357,7 @@
         <v>14</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C82" t="s" s="2">
         <v>14</v>
@@ -3375,7 +3375,7 @@
         <v>14</v>
       </c>
       <c r="H82" t="s" s="2">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I82" t="s" s="2">
         <v>19</v>
@@ -3384,7 +3384,7 @@
         <v>14</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="83">
@@ -3392,7 +3392,7 @@
         <v>14</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C83" t="s" s="2">
         <v>14</v>
@@ -3410,7 +3410,7 @@
         <v>14</v>
       </c>
       <c r="H83" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I83" t="s" s="2">
         <v>19</v>
@@ -3419,7 +3419,7 @@
         <v>14</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="84">
@@ -3427,7 +3427,7 @@
         <v>14</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C84" t="s" s="2">
         <v>14</v>
@@ -3445,7 +3445,7 @@
         <v>14</v>
       </c>
       <c r="H84" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I84" t="s" s="2">
         <v>19</v>
@@ -3454,7 +3454,7 @@
         <v>14</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="85">
@@ -3462,7 +3462,7 @@
         <v>14</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C85" t="s" s="2">
         <v>14</v>
@@ -3480,7 +3480,7 @@
         <v>14</v>
       </c>
       <c r="H85" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I85" t="s" s="2">
         <v>19</v>
@@ -3489,7 +3489,7 @@
         <v>14</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="86">
@@ -3497,7 +3497,7 @@
         <v>14</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C86" t="s" s="2">
         <v>14</v>
@@ -3515,7 +3515,7 @@
         <v>14</v>
       </c>
       <c r="H86" t="s" s="2">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I86" t="s" s="2">
         <v>19</v>
@@ -3532,7 +3532,7 @@
         <v>14</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C87" t="s" s="2">
         <v>14</v>
@@ -3550,16 +3550,16 @@
         <v>14</v>
       </c>
       <c r="H87" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="I87" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J87" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K87" t="s" s="2">
         <v>45</v>
-      </c>
-      <c r="I87" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="J87" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="K87" t="s" s="2">
-        <v>46</v>
       </c>
     </row>
     <row r="88">
@@ -3567,7 +3567,7 @@
         <v>14</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C88" t="s" s="2">
         <v>14</v>
@@ -3585,16 +3585,16 @@
         <v>14</v>
       </c>
       <c r="H88" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="I88" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J88" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K88" t="s" s="2">
         <v>47</v>
-      </c>
-      <c r="I88" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="J88" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="K88" t="s" s="2">
-        <v>48</v>
       </c>
     </row>
     <row r="89">
@@ -3602,7 +3602,7 @@
         <v>14</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C89" t="s" s="2">
         <v>14</v>
@@ -3620,7 +3620,7 @@
         <v>14</v>
       </c>
       <c r="H89" t="s" s="2">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I89" t="s" s="2">
         <v>19</v>
@@ -3629,7 +3629,7 @@
         <v>14</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="90">
@@ -3637,7 +3637,7 @@
         <v>14</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C90" t="s" s="2">
         <v>14</v>
@@ -3655,7 +3655,7 @@
         <v>14</v>
       </c>
       <c r="H90" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I90" t="s" s="2">
         <v>19</v>
@@ -3664,15 +3664,15 @@
         <v>14</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="B91" t="s" s="2">
         <v>88</v>
-      </c>
-      <c r="B91" t="s" s="2">
-        <v>89</v>
       </c>
       <c r="C91" t="s" s="2">
         <v>13</v>
@@ -3681,13 +3681,13 @@
         <v>14</v>
       </c>
       <c r="E91" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F91" t="s" s="2">
         <v>16</v>
       </c>
       <c r="G91" t="s" s="2">
-        <v>17</v>
+        <v>90</v>
       </c>
       <c r="H91" t="s" s="2">
         <v>18</v>
@@ -3722,7 +3722,7 @@
         <v>16</v>
       </c>
       <c r="G92" t="s" s="2">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="H92" t="s" s="2">
         <v>18</v>
@@ -3757,7 +3757,7 @@
         <v>16</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>17</v>
+        <v>90</v>
       </c>
       <c r="H93" t="s" s="2">
         <v>18</v>
@@ -3792,7 +3792,7 @@
         <v>16</v>
       </c>
       <c r="G94" t="s" s="2">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="H94" t="s" s="2">
         <v>18</v>
@@ -3827,7 +3827,7 @@
         <v>16</v>
       </c>
       <c r="G95" t="s" s="2">
-        <v>17</v>
+        <v>90</v>
       </c>
       <c r="H95" t="s" s="2">
         <v>18</v>
@@ -3850,7 +3850,7 @@
         <v>104</v>
       </c>
       <c r="C96" t="s" s="2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D96" t="s" s="2">
         <v>14</v>
@@ -3859,13 +3859,13 @@
         <v>14</v>
       </c>
       <c r="F96" t="s" s="2">
+        <v>27</v>
+      </c>
+      <c r="G96" t="s" s="2">
         <v>28</v>
       </c>
-      <c r="G96" t="s" s="2">
-        <v>29</v>
-      </c>
       <c r="H96" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I96" t="s" s="2">
         <v>19</v>
@@ -3900,7 +3900,7 @@
         <v>14</v>
       </c>
       <c r="H97" t="s" s="2">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I97" t="s" s="2">
         <v>19</v>
@@ -3909,7 +3909,7 @@
         <v>14</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="98">
@@ -3935,7 +3935,7 @@
         <v>14</v>
       </c>
       <c r="H98" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I98" t="s" s="2">
         <v>19</v>
@@ -3944,7 +3944,7 @@
         <v>14</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="99">
@@ -3970,7 +3970,7 @@
         <v>14</v>
       </c>
       <c r="H99" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I99" t="s" s="2">
         <v>19</v>
@@ -3979,7 +3979,7 @@
         <v>14</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="100">
@@ -4005,7 +4005,7 @@
         <v>14</v>
       </c>
       <c r="H100" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I100" t="s" s="2">
         <v>19</v>
@@ -4014,7 +4014,7 @@
         <v>14</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="101">
@@ -4040,7 +4040,7 @@
         <v>14</v>
       </c>
       <c r="H101" t="s" s="2">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I101" t="s" s="2">
         <v>19</v>
@@ -4075,16 +4075,16 @@
         <v>14</v>
       </c>
       <c r="H102" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="I102" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J102" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K102" t="s" s="2">
         <v>45</v>
-      </c>
-      <c r="I102" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="J102" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="K102" t="s" s="2">
-        <v>46</v>
       </c>
     </row>
     <row r="103">
@@ -4110,16 +4110,16 @@
         <v>14</v>
       </c>
       <c r="H103" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="I103" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J103" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K103" t="s" s="2">
         <v>47</v>
-      </c>
-      <c r="I103" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="J103" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="K103" t="s" s="2">
-        <v>48</v>
       </c>
     </row>
     <row r="104">
@@ -4145,7 +4145,7 @@
         <v>14</v>
       </c>
       <c r="H104" t="s" s="2">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I104" t="s" s="2">
         <v>19</v>
@@ -4154,7 +4154,7 @@
         <v>14</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="105">
@@ -4180,7 +4180,7 @@
         <v>14</v>
       </c>
       <c r="H105" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I105" t="s" s="2">
         <v>19</v>
@@ -4189,7 +4189,7 @@
         <v>14</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="106">
@@ -4200,7 +4200,7 @@
         <v>106</v>
       </c>
       <c r="C106" t="s" s="2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D106" t="s" s="2">
         <v>14</v>
@@ -4209,10 +4209,10 @@
         <v>14</v>
       </c>
       <c r="F106" t="s" s="2">
+        <v>27</v>
+      </c>
+      <c r="G106" t="s" s="2">
         <v>28</v>
-      </c>
-      <c r="G106" t="s" s="2">
-        <v>29</v>
       </c>
       <c r="H106" t="s" s="2">
         <v>14</v>
@@ -4250,7 +4250,7 @@
         <v>14</v>
       </c>
       <c r="H107" t="s" s="2">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I107" t="s" s="2">
         <v>19</v>
@@ -4259,7 +4259,7 @@
         <v>14</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="108">
@@ -4285,7 +4285,7 @@
         <v>14</v>
       </c>
       <c r="H108" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I108" t="s" s="2">
         <v>19</v>
@@ -4294,7 +4294,7 @@
         <v>14</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="109">
@@ -4320,7 +4320,7 @@
         <v>14</v>
       </c>
       <c r="H109" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I109" t="s" s="2">
         <v>19</v>
@@ -4329,7 +4329,7 @@
         <v>14</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="110">
@@ -4355,7 +4355,7 @@
         <v>14</v>
       </c>
       <c r="H110" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I110" t="s" s="2">
         <v>19</v>
@@ -4390,7 +4390,7 @@
         <v>14</v>
       </c>
       <c r="H111" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I111" t="s" s="2">
         <v>19</v>
@@ -4399,7 +4399,7 @@
         <v>14</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="112">
@@ -4410,7 +4410,7 @@
         <v>108</v>
       </c>
       <c r="C112" t="s" s="2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D112" t="s" s="2">
         <v>14</v>
@@ -4419,13 +4419,13 @@
         <v>109</v>
       </c>
       <c r="F112" t="s" s="2">
+        <v>27</v>
+      </c>
+      <c r="G112" t="s" s="2">
         <v>28</v>
       </c>
-      <c r="G112" t="s" s="2">
-        <v>29</v>
-      </c>
       <c r="H112" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I112" t="s" s="2">
         <v>19</v>
@@ -4460,7 +4460,7 @@
         <v>14</v>
       </c>
       <c r="H113" t="s" s="2">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I113" t="s" s="2">
         <v>19</v>
@@ -4469,7 +4469,7 @@
         <v>14</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="114">
@@ -4495,7 +4495,7 @@
         <v>14</v>
       </c>
       <c r="H114" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I114" t="s" s="2">
         <v>19</v>
@@ -4504,7 +4504,7 @@
         <v>14</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="115">
@@ -4530,7 +4530,7 @@
         <v>14</v>
       </c>
       <c r="H115" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I115" t="s" s="2">
         <v>19</v>
@@ -4539,7 +4539,7 @@
         <v>14</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="116">
@@ -4565,7 +4565,7 @@
         <v>14</v>
       </c>
       <c r="H116" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I116" t="s" s="2">
         <v>19</v>
@@ -4574,7 +4574,7 @@
         <v>14</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="117">
@@ -4600,7 +4600,7 @@
         <v>14</v>
       </c>
       <c r="H117" t="s" s="2">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I117" t="s" s="2">
         <v>19</v>
@@ -4635,16 +4635,16 @@
         <v>14</v>
       </c>
       <c r="H118" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="I118" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J118" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K118" t="s" s="2">
         <v>45</v>
-      </c>
-      <c r="I118" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="J118" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="K118" t="s" s="2">
-        <v>46</v>
       </c>
     </row>
     <row r="119">
@@ -4670,16 +4670,16 @@
         <v>14</v>
       </c>
       <c r="H119" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="I119" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J119" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K119" t="s" s="2">
         <v>47</v>
-      </c>
-      <c r="I119" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="J119" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="K119" t="s" s="2">
-        <v>48</v>
       </c>
     </row>
     <row r="120">
@@ -4705,7 +4705,7 @@
         <v>14</v>
       </c>
       <c r="H120" t="s" s="2">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I120" t="s" s="2">
         <v>19</v>
@@ -4714,7 +4714,7 @@
         <v>14</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="121">
@@ -4740,7 +4740,7 @@
         <v>14</v>
       </c>
       <c r="H121" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I121" t="s" s="2">
         <v>19</v>
@@ -4749,7 +4749,7 @@
         <v>14</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="122">
@@ -4760,7 +4760,7 @@
         <v>111</v>
       </c>
       <c r="C122" t="s" s="2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D122" t="s" s="2">
         <v>14</v>
@@ -4769,13 +4769,13 @@
         <v>112</v>
       </c>
       <c r="F122" t="s" s="2">
+        <v>27</v>
+      </c>
+      <c r="G122" t="s" s="2">
         <v>28</v>
       </c>
-      <c r="G122" t="s" s="2">
-        <v>29</v>
-      </c>
       <c r="H122" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I122" t="s" s="2">
         <v>19</v>
@@ -4810,7 +4810,7 @@
         <v>14</v>
       </c>
       <c r="H123" t="s" s="2">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I123" t="s" s="2">
         <v>19</v>
@@ -4819,7 +4819,7 @@
         <v>14</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="124">
@@ -4845,7 +4845,7 @@
         <v>14</v>
       </c>
       <c r="H124" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I124" t="s" s="2">
         <v>19</v>
@@ -4854,7 +4854,7 @@
         <v>14</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="125">
@@ -4880,7 +4880,7 @@
         <v>14</v>
       </c>
       <c r="H125" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I125" t="s" s="2">
         <v>19</v>
@@ -4889,7 +4889,7 @@
         <v>14</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="126">
@@ -4915,7 +4915,7 @@
         <v>14</v>
       </c>
       <c r="H126" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I126" t="s" s="2">
         <v>19</v>
@@ -4924,7 +4924,7 @@
         <v>14</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="127">
@@ -4950,7 +4950,7 @@
         <v>14</v>
       </c>
       <c r="H127" t="s" s="2">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I127" t="s" s="2">
         <v>19</v>
@@ -4985,16 +4985,16 @@
         <v>14</v>
       </c>
       <c r="H128" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="I128" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J128" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K128" t="s" s="2">
         <v>45</v>
-      </c>
-      <c r="I128" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="J128" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="K128" t="s" s="2">
-        <v>46</v>
       </c>
     </row>
     <row r="129">
@@ -5020,16 +5020,16 @@
         <v>14</v>
       </c>
       <c r="H129" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="I129" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J129" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K129" t="s" s="2">
         <v>47</v>
-      </c>
-      <c r="I129" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="J129" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="K129" t="s" s="2">
-        <v>48</v>
       </c>
     </row>
     <row r="130">
@@ -5055,7 +5055,7 @@
         <v>14</v>
       </c>
       <c r="H130" t="s" s="2">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I130" t="s" s="2">
         <v>19</v>
@@ -5064,7 +5064,7 @@
         <v>14</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="131">
@@ -5090,7 +5090,7 @@
         <v>14</v>
       </c>
       <c r="H131" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I131" t="s" s="2">
         <v>19</v>
@@ -5099,7 +5099,7 @@
         <v>14</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="132">
@@ -5110,7 +5110,7 @@
         <v>114</v>
       </c>
       <c r="C132" t="s" s="2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D132" t="s" s="2">
         <v>14</v>
@@ -5119,13 +5119,13 @@
         <v>115</v>
       </c>
       <c r="F132" t="s" s="2">
+        <v>27</v>
+      </c>
+      <c r="G132" t="s" s="2">
         <v>28</v>
       </c>
-      <c r="G132" t="s" s="2">
-        <v>29</v>
-      </c>
       <c r="H132" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I132" t="s" s="2">
         <v>19</v>
@@ -5160,7 +5160,7 @@
         <v>14</v>
       </c>
       <c r="H133" t="s" s="2">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I133" t="s" s="2">
         <v>19</v>
@@ -5169,7 +5169,7 @@
         <v>14</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="134">
@@ -5195,7 +5195,7 @@
         <v>14</v>
       </c>
       <c r="H134" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I134" t="s" s="2">
         <v>19</v>
@@ -5204,7 +5204,7 @@
         <v>14</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="135">
@@ -5230,7 +5230,7 @@
         <v>14</v>
       </c>
       <c r="H135" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I135" t="s" s="2">
         <v>19</v>
@@ -5239,7 +5239,7 @@
         <v>14</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="136">
@@ -5265,7 +5265,7 @@
         <v>14</v>
       </c>
       <c r="H136" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I136" t="s" s="2">
         <v>19</v>
@@ -5274,7 +5274,7 @@
         <v>14</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="137">
@@ -5300,7 +5300,7 @@
         <v>14</v>
       </c>
       <c r="H137" t="s" s="2">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I137" t="s" s="2">
         <v>19</v>
@@ -5335,16 +5335,16 @@
         <v>14</v>
       </c>
       <c r="H138" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="I138" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J138" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K138" t="s" s="2">
         <v>45</v>
-      </c>
-      <c r="I138" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="J138" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="K138" t="s" s="2">
-        <v>46</v>
       </c>
     </row>
     <row r="139">
@@ -5370,16 +5370,16 @@
         <v>14</v>
       </c>
       <c r="H139" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="I139" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J139" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K139" t="s" s="2">
         <v>47</v>
-      </c>
-      <c r="I139" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="J139" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="K139" t="s" s="2">
-        <v>48</v>
       </c>
     </row>
     <row r="140">
@@ -5405,7 +5405,7 @@
         <v>14</v>
       </c>
       <c r="H140" t="s" s="2">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I140" t="s" s="2">
         <v>19</v>
@@ -5414,7 +5414,7 @@
         <v>14</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="141">
@@ -5440,7 +5440,7 @@
         <v>14</v>
       </c>
       <c r="H141" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I141" t="s" s="2">
         <v>19</v>
@@ -5449,7 +5449,7 @@
         <v>14</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="142">
@@ -5460,7 +5460,7 @@
         <v>117</v>
       </c>
       <c r="C142" t="s" s="2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D142" t="s" s="2">
         <v>14</v>
@@ -5469,13 +5469,13 @@
         <v>118</v>
       </c>
       <c r="F142" t="s" s="2">
+        <v>27</v>
+      </c>
+      <c r="G142" t="s" s="2">
         <v>28</v>
       </c>
-      <c r="G142" t="s" s="2">
-        <v>29</v>
-      </c>
       <c r="H142" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I142" t="s" s="2">
         <v>19</v>
@@ -5510,7 +5510,7 @@
         <v>14</v>
       </c>
       <c r="H143" t="s" s="2">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I143" t="s" s="2">
         <v>19</v>
@@ -5519,7 +5519,7 @@
         <v>14</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="144">
@@ -5545,7 +5545,7 @@
         <v>14</v>
       </c>
       <c r="H144" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I144" t="s" s="2">
         <v>19</v>
@@ -5554,7 +5554,7 @@
         <v>14</v>
       </c>
       <c r="K144" t="s" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="145">
@@ -5580,7 +5580,7 @@
         <v>14</v>
       </c>
       <c r="H145" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I145" t="s" s="2">
         <v>19</v>
@@ -5589,7 +5589,7 @@
         <v>14</v>
       </c>
       <c r="K145" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="146">
@@ -5615,7 +5615,7 @@
         <v>14</v>
       </c>
       <c r="H146" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I146" t="s" s="2">
         <v>19</v>
@@ -5624,7 +5624,7 @@
         <v>14</v>
       </c>
       <c r="K146" t="s" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="147">
@@ -5650,7 +5650,7 @@
         <v>14</v>
       </c>
       <c r="H147" t="s" s="2">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I147" t="s" s="2">
         <v>19</v>
@@ -5685,16 +5685,16 @@
         <v>14</v>
       </c>
       <c r="H148" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="I148" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J148" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K148" t="s" s="2">
         <v>45</v>
-      </c>
-      <c r="I148" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="J148" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="K148" t="s" s="2">
-        <v>46</v>
       </c>
     </row>
     <row r="149">
@@ -5720,16 +5720,16 @@
         <v>14</v>
       </c>
       <c r="H149" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="I149" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J149" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K149" t="s" s="2">
         <v>47</v>
-      </c>
-      <c r="I149" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="J149" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="K149" t="s" s="2">
-        <v>48</v>
       </c>
     </row>
     <row r="150">
@@ -5755,7 +5755,7 @@
         <v>14</v>
       </c>
       <c r="H150" t="s" s="2">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I150" t="s" s="2">
         <v>19</v>
@@ -5764,7 +5764,7 @@
         <v>14</v>
       </c>
       <c r="K150" t="s" s="2">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="151">
@@ -5790,7 +5790,7 @@
         <v>14</v>
       </c>
       <c r="H151" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I151" t="s" s="2">
         <v>19</v>
@@ -5799,7 +5799,7 @@
         <v>14</v>
       </c>
       <c r="K151" t="s" s="2">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="152">
@@ -5810,7 +5810,7 @@
         <v>120</v>
       </c>
       <c r="C152" t="s" s="2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D152" t="s" s="2">
         <v>14</v>
@@ -5819,13 +5819,13 @@
         <v>121</v>
       </c>
       <c r="F152" t="s" s="2">
+        <v>27</v>
+      </c>
+      <c r="G152" t="s" s="2">
         <v>28</v>
       </c>
-      <c r="G152" t="s" s="2">
-        <v>29</v>
-      </c>
       <c r="H152" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I152" t="s" s="2">
         <v>19</v>
@@ -5860,7 +5860,7 @@
         <v>14</v>
       </c>
       <c r="H153" t="s" s="2">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I153" t="s" s="2">
         <v>19</v>
@@ -5869,7 +5869,7 @@
         <v>14</v>
       </c>
       <c r="K153" t="s" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="154">
@@ -5895,7 +5895,7 @@
         <v>14</v>
       </c>
       <c r="H154" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I154" t="s" s="2">
         <v>19</v>
@@ -5904,7 +5904,7 @@
         <v>14</v>
       </c>
       <c r="K154" t="s" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="155">
@@ -5930,7 +5930,7 @@
         <v>14</v>
       </c>
       <c r="H155" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I155" t="s" s="2">
         <v>19</v>
@@ -5939,7 +5939,7 @@
         <v>14</v>
       </c>
       <c r="K155" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="156">
@@ -5965,7 +5965,7 @@
         <v>14</v>
       </c>
       <c r="H156" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I156" t="s" s="2">
         <v>19</v>
@@ -5974,7 +5974,7 @@
         <v>14</v>
       </c>
       <c r="K156" t="s" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="157">
@@ -6000,7 +6000,7 @@
         <v>14</v>
       </c>
       <c r="H157" t="s" s="2">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I157" t="s" s="2">
         <v>19</v>
@@ -6035,16 +6035,16 @@
         <v>14</v>
       </c>
       <c r="H158" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="I158" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J158" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K158" t="s" s="2">
         <v>45</v>
-      </c>
-      <c r="I158" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="J158" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="K158" t="s" s="2">
-        <v>46</v>
       </c>
     </row>
     <row r="159">
@@ -6070,16 +6070,16 @@
         <v>14</v>
       </c>
       <c r="H159" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="I159" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J159" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K159" t="s" s="2">
         <v>47</v>
-      </c>
-      <c r="I159" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="J159" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="K159" t="s" s="2">
-        <v>48</v>
       </c>
     </row>
     <row r="160">
@@ -6105,7 +6105,7 @@
         <v>14</v>
       </c>
       <c r="H160" t="s" s="2">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I160" t="s" s="2">
         <v>19</v>
@@ -6114,7 +6114,7 @@
         <v>14</v>
       </c>
       <c r="K160" t="s" s="2">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="161">
@@ -6140,7 +6140,7 @@
         <v>14</v>
       </c>
       <c r="H161" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I161" t="s" s="2">
         <v>19</v>
@@ -6149,7 +6149,7 @@
         <v>14</v>
       </c>
       <c r="K161" t="s" s="2">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
